--- a/ukraina_biznesy_sait_500usd_leads.xlsx
+++ b/ukraina_biznesy_sait_500usd_leads.xlsx
@@ -59348,7 +59348,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-22T20:25:20</t>
+          <t>2026-05-22T20:25:50</t>
         </is>
       </c>
     </row>
@@ -59384,7 +59384,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Частина записів — прямі запити (Freelancehunt, Work.ua тощо), частина — кваліфіковані потенційні ліди за профілем мікробізнесу. Рекомендується верифікація перед продажем.</t>
+          <t>Прямі запити: FL.ru, Kwork (рівень впевненості середній/високий). ФОП з ЄДР — реальні суб'єкти, реєстрація з 2020 р. (низький рівень — потрібна верифікація потреби).</t>
         </is>
       </c>
     </row>
